--- a/JsonConverter/ExcelFiles/UnlockConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/UnlockConditionData.xlsx
@@ -19,51 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <x:si>
-    <x:t>Count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item_aaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 aaa보유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_win_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WinStreak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 1승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HasItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5연승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetId</x:t>
+    <x:t>3연승</x:t>
   </x:si>
   <x:si>
     <x:t>cond_streak_3</x:t>
@@ -73,6 +31,54 @@
   </x:si>
   <x:si>
     <x:t>cond_item_aaa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Count</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HasItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 1승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WinStreak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_win_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 aaa보유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>item_aaa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -859,81 +865,93 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:1" ht="13.199999999999999">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/UnlockConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/UnlockConditionData.xlsx
@@ -19,7 +19,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+  <x:si>
+    <x:t>5연승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_streak_5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_win_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WinStreak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>item_aaa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 aaa보유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HasItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Count</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 1승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
   <x:si>
     <x:t>3연승</x:t>
   </x:si>
@@ -27,58 +81,10 @@
     <x:t>cond_streak_3</x:t>
   </x:si>
   <x:si>
+    <x:t>cond_item_aaa</x:t>
+  </x:si>
+  <x:si>
     <x:t>TotalWinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_item_aaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HasItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 1승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WinStreak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_win_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 aaa보유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item_aaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -865,99 +871,111 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C4" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A7" s="5"/>
-      <x:c r="B7" s="5"/>
-      <x:c r="C7" s="5"/>
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A7" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="5">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A8" s="5"/>

--- a/JsonConverter/ExcelFiles/UnlockConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/UnlockConditionData.xlsx
@@ -19,14 +19,44 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+  <x:si>
+    <x:t>cond_win_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3연승</x:t>
+  </x:si>
   <x:si>
     <x:t>5연승</x:t>
   </x:si>
   <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>cond_streak_5</x:t>
   </x:si>
   <x:si>
+    <x:t>cond_item_aaa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TotalWinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_streak_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 aaa보유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>item_aaa</x:t>
+  </x:si>
+  <x:si>
     <x:t>cond_win_1</x:t>
   </x:si>
   <x:si>
@@ -36,55 +66,31 @@
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>TargetId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item_aaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 aaa보유</x:t>
-  </x:si>
-  <x:si>
     <x:t>Type</x:t>
   </x:si>
   <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>HasItem</x:t>
   </x:si>
   <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 1승</x:t>
+  </x:si>
+  <x:si>
     <x:t>Count</x:t>
   </x:si>
   <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 1승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3연승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_streak_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_item_aaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TotalWinCount</x:t>
+    <x:t>전체 3승</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -226,7 +232,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -249,6 +255,9 @@
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -855,7 +864,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:F35"/>
+  <x:dimension ref="A1:F36"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -871,141 +880,154 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F4" s="4"/>
     </x:row>
-    <x:row r="5" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F5" s="8"/>
     </x:row>
     <x:row r="6" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="3">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A7" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C7" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C6" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A7" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B7" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="5">
+    </x:row>
+    <x:row r="8" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A8" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A8" s="5"/>
-      <x:c r="B8" s="5"/>
-      <x:c r="C8" s="5"/>
+      <x:c r="B8" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="5">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A9" s="5"/>
       <x:c r="B9" s="5"/>
       <x:c r="C9" s="5"/>
     </x:row>
-    <x:row r="10" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A10" s="5"/>
+      <x:c r="B10" s="5"/>
+      <x:c r="C10" s="5"/>
+    </x:row>
     <x:row r="11" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
-    </x:row>
+    <x:row r="12" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A13" s="3"/>
-      <x:c r="B13" s="3"/>
-      <x:c r="C13" s="3"/>
-    </x:row>
-    <x:row r="14" ht="15.75" customHeight="1"/>
+      <x:c r="A13" s="6"/>
+      <x:c r="B13" s="6"/>
+      <x:c r="C13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A14" s="3"/>
+      <x:c r="B14" s="3"/>
+      <x:c r="C14" s="3"/>
+    </x:row>
     <x:row r="15" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="5"/>
-      <x:c r="B16" s="5"/>
-      <x:c r="C16" s="5"/>
-    </x:row>
+    <x:row r="16" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A17" s="5"/>
       <x:c r="B17" s="5"/>
@@ -1052,9 +1074,9 @@
       <x:c r="C25" s="5"/>
     </x:row>
     <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="6"/>
-      <x:c r="B26" s="6"/>
-      <x:c r="C26" s="6"/>
+      <x:c r="A26" s="5"/>
+      <x:c r="B26" s="5"/>
+      <x:c r="C26" s="5"/>
     </x:row>
     <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A27" s="6"/>
@@ -1082,9 +1104,9 @@
       <x:c r="C31" s="6"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="3"/>
-      <x:c r="B32" s="3"/>
-      <x:c r="C32" s="3"/>
+      <x:c r="A32" s="6"/>
+      <x:c r="B32" s="6"/>
+      <x:c r="C32" s="6"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A33" s="3"/>
@@ -1101,7 +1123,11 @@
       <x:c r="B35" s="3"/>
       <x:c r="C35" s="3"/>
     </x:row>
-    <x:row r="36" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A36" s="3"/>
+      <x:c r="B36" s="3"/>
+      <x:c r="C36" s="3"/>
+    </x:row>
     <x:row r="37" ht="15.75" customHeight="1"/>
     <x:row r="38" ht="15.75" customHeight="1"/>
     <x:row r="39" ht="15.75" customHeight="1"/>
@@ -2066,6 +2092,7 @@
     <x:row r="998" ht="15.75" customHeight="1"/>
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
+    <x:row r="1001" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/JsonConverter/ExcelFiles/UnlockConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/UnlockConditionData.xlsx
@@ -19,78 +19,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+  <x:si>
+    <x:t>StandingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3연승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5연승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주짓수 공격 스탯 200 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스탠딩 타격 스탯 150 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링 공격 스탯 200 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FighterStatAtLeast</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WinStreak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_win_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 3승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Count</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HasItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 1승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_item_aaa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_streak_5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_streak_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TotalWinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스탠딩 타격 스탯 50 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 aaa보유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>item_aaa</x:t>
+  </x:si>
   <x:si>
     <x:t>cond_win_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3연승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5연승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_streak_5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_item_aaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TotalWinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_streak_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 aaa보유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item_aaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_win_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WinStreak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HasItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 1승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 3승</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -880,41 +916,41 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>9</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
@@ -922,100 +958,156 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="8"/>
     </x:row>
     <x:row r="6" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="5">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5"/>
-      <x:c r="B9" s="5"/>
-      <x:c r="C9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A10" s="5"/>
-      <x:c r="B10" s="5"/>
-      <x:c r="C10" s="5"/>
-    </x:row>
-    <x:row r="11" ht="15.75" customHeight="1"/>
-    <x:row r="12" ht="15.75" customHeight="1"/>
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="5">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A10" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="5">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A11" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="1">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A12" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B12" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="1">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
     <x:row r="13" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A13" s="6"/>
       <x:c r="B13" s="6"/>
